--- a/artfynd/A 41266-2021 artfynd.xlsx
+++ b/artfynd/A 41266-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41266-2021 artfynd.xlsx
+++ b/artfynd/A 41266-2021 artfynd.xlsx
@@ -4047,7 +4047,7 @@
         <v>126839410</v>
       </c>
       <c r="B26" t="n">
-        <v>56596</v>
+        <v>56600</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 41266-2021 artfynd.xlsx
+++ b/artfynd/A 41266-2021 artfynd.xlsx
@@ -4047,7 +4047,7 @@
         <v>126839410</v>
       </c>
       <c r="B26" t="n">
-        <v>56600</v>
+        <v>56596</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 41266-2021 artfynd.xlsx
+++ b/artfynd/A 41266-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104165878</v>
+        <v>126839410</v>
       </c>
       <c r="B2" t="n">
-        <v>5207</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100155</v>
+        <v>100041</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre timmerman</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Acanthocinus griseus</t>
+          <t>Coronella austriaca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
+          <t>Laurenti, 1768</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,17 +711,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Finsjöbrännan, Sm</t>
+          <t>Skvalbäcken, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575416</v>
+        <v>575468</v>
       </c>
       <c r="R2" t="n">
-        <v>6336378</v>
+        <v>6336200</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,49 +766,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Olof Persson</t>
+          <t>Marcus Arnesson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olof Persson, Jesper Hansson</t>
+          <t>Marcus Arnesson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104165887</v>
+        <v>104688012</v>
       </c>
       <c r="B3" t="n">
-        <v>7589</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4997</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106431</v>
+        <v>100517</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Furuvedvivel</t>
+          <t>Åttafläckig praktbagge</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhyncolus elongatus</t>
+          <t>Buprestis octoguttata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575416.4329915076</v>
+        <v>575416</v>
       </c>
       <c r="R3" t="n">
-        <v>6336378.137707204</v>
+        <v>6336378</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,19 +851,14 @@
           <t>2022-06-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-10</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Insamlade under NCG-träff</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,58 +886,62 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104688012</v>
+        <v>108690566</v>
       </c>
       <c r="B4" t="n">
-        <v>4934</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>12861</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100517</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Åttafläckig praktbagge</t>
-        </is>
+        <v>100701</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buprestis octoguttata</t>
+          <t>Colydium elongatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Finsjöbrännan, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575416.4329915076</v>
+        <v>575452</v>
       </c>
       <c r="R4" t="n">
-        <v>6336378.137707204</v>
+        <v>6336295</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,27 +965,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Insamlade under NCG-träff</t>
+          <t>Inventering utförd av länsstyrelsen i Kalmar län.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +984,15 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bränd, död ek</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1020,19 +1004,18 @@
           <t>Olof Persson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106216655</v>
+        <v>108690562</v>
       </c>
       <c r="B5" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6302</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,21 +1023,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102004</v>
+        <v>100838</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ekgetingbock</t>
+          <t>Enfärgad brandsvampbagge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Xylotrechus antilope</t>
+          <t>Diplocoelus fagi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schönherr, 1817)</t>
+          <t>(Chevrolat, 1837)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1062,6 +1045,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>fönsterfälla</t>
@@ -1073,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575461.6290098059</v>
+        <v>575452</v>
       </c>
       <c r="R5" t="n">
-        <v>6336284.051757373</v>
+        <v>6336295</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,19 +1099,14 @@
           <t>2022-07-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Inventering utförd av länsstyrelsen i Kalmar län.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,25 +1118,21 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>branddödad björk</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>Michael Tholin</t>
-        </is>
-      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bränd, död ek</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Olof Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Olof Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1159,15 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106295826</v>
+        <v>108690982</v>
       </c>
       <c r="B6" t="n">
-        <v>19408</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>12521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,36 +1154,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102078</v>
+        <v>101141</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blankpannad kalögonbroms</t>
+          <t>Glänsande blombagge</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tabanus glaucopis</t>
+          <t>Ischnomera caerulea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Meigen, 1820</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>malaisefälla</t>
+          <t>fönsterfälla</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1213,10 +1197,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575453.4503752812</v>
+        <v>575461</v>
       </c>
       <c r="R6" t="n">
-        <v>6336285.529188555</v>
+        <v>6336284</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,22 +1227,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Inventering utförd av länsstyrelsen i Kalmar län.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,24 +1246,24 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>Sven Hellqvist</t>
-        </is>
-      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Grov, bränd, död björk</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Olof Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Michael Tholin</t>
+          <t>Olof Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1298,16 +1277,11 @@
         <v>108690319</v>
       </c>
       <c r="B7" t="n">
-        <v>11968</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>12082</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1349,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575452.1753613513</v>
+        <v>575452</v>
       </c>
       <c r="R7" t="n">
-        <v>6336295.810780574</v>
+        <v>6336295</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,19 +1356,9 @@
           <t>2022-05-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1436,42 +1400,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>108690326</v>
+        <v>104165850</v>
       </c>
       <c r="B8" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5009</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102004</v>
+        <v>101284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ekgetingbock</t>
+          <t>Sotpraktbagge</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Xylotrechus antilope</t>
+          <t>Melanophila acuminata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schönherr, 1817)</t>
+          <t>(De Geer, 1774)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1484,24 +1443,22 @@
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Finsjöbrännan, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575452.1753613513</v>
+        <v>575416</v>
       </c>
       <c r="R8" t="n">
-        <v>6336295.810780574</v>
+        <v>6336378</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1525,27 +1482,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-05-18</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Inventering utförd av länsstyrelsen i Kalmar län.</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1554,15 +1496,10 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bränd, död ek</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1574,45 +1511,41 @@
           <t>Olof Persson</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
-        </is>
-      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>108690566</v>
+        <v>108690325</v>
       </c>
       <c r="B9" t="n">
-        <v>12743</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5009</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100701</v>
+        <v>101284</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sotpraktbagge</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Colydium elongatum</t>
+          <t>Melanophila acuminata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(De Geer, 1774)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1636,10 +1569,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575452.1753613513</v>
+        <v>575452</v>
       </c>
       <c r="R9" t="n">
-        <v>6336295.810780574</v>
+        <v>6336295</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1666,22 +1599,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
+          <t>2022-05-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
           <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2022-08-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1723,42 +1646,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>108689757</v>
+        <v>108690253</v>
       </c>
       <c r="B10" t="n">
-        <v>8209</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6778</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101592</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Ekcylinderbagge</t>
-        </is>
+        <v>101413</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platypus cylindrus</t>
+          <t>Notolaemus unifasciatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
+          <t>(Latreille, 1804)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1773,7 +1686,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>malaisefälla</t>
+          <t>fönsterfälla</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1782,10 +1695,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575453.4503752812</v>
+        <v>575461</v>
       </c>
       <c r="R10" t="n">
-        <v>6336285.529188555</v>
+        <v>6336284</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1812,22 +1725,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1843,6 +1746,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Grov, bränd, död björk</t>
+        </is>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AT10" t="inlineStr"/>
@@ -1864,37 +1772,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>108690564</v>
+        <v>108690301</v>
       </c>
       <c r="B11" t="n">
-        <v>9073</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6778</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101595</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Aspstumpbagge</t>
-        </is>
+        <v>101413</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platysoma deplanatum</t>
+          <t>Notolaemus unifasciatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1808)</t>
+          <t>(Latreille, 1804)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1923,10 +1821,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575452.1753613513</v>
+        <v>575452</v>
       </c>
       <c r="R11" t="n">
-        <v>6336295.810780574</v>
+        <v>6336295</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1953,22 +1851,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>2022-05-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
           <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2022-08-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2010,15 +1898,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>108690996</v>
+        <v>108690564</v>
       </c>
       <c r="B12" t="n">
-        <v>7102</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9178</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2026,21 +1909,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101593</v>
+        <v>101595</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Storplattnos</t>
+          <t>Aspstumpbagge</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platyrhinus resinosus</t>
+          <t>Platysoma deplanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Gyllenhal, 1808)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2069,10 +1952,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575461.6290098059</v>
+        <v>575452</v>
       </c>
       <c r="R12" t="n">
-        <v>6336284.051757373</v>
+        <v>6336295</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2099,22 +1982,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-05-18</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2133,7 +2006,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Grov, bränd, död björk</t>
+          <t>Bränd, död ek</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr"/>
@@ -2156,57 +2029,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>108690561</v>
+        <v>106295826</v>
       </c>
       <c r="B13" t="n">
-        <v>5219</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>19694</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102147</v>
+        <v>102078</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelbock</t>
+          <t>Blankpannad kalögonbroms</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Aegomorphus clavipes</t>
+          <t>Tabanus glaucopis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schrank, 1781)</t>
+          <t>Meigen, 1820</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>fönsterfälla</t>
+          <t>malaisefälla</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2215,10 +2078,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575452.1753613513</v>
+        <v>575454</v>
       </c>
       <c r="R13" t="n">
-        <v>6336295.810780574</v>
+        <v>6336286</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2245,27 +2108,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Inventering utförd av länsstyrelsen i Kalmar län.</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2274,24 +2122,24 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bränd, död ek</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>Sven Hellqvist</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Olof Persson</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Olof Persson</t>
+          <t>Via Michael Tholin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2302,42 +2150,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>108690246</v>
+        <v>108690330</v>
       </c>
       <c r="B14" t="n">
-        <v>8395</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5288</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101988</v>
+        <v>102147</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattad lövvedborre</t>
+          <t>Spindelbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Xyleborus monographus</t>
+          <t>Aegomorphus clavipes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
+          <t>(Schrank, 1781)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2361,10 +2204,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575461.6290098059</v>
+        <v>575452</v>
       </c>
       <c r="R14" t="n">
-        <v>6336284.051757373</v>
+        <v>6336295</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2391,12 +2234,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-05-18</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2404,11 +2242,6 @@
           <t>2022-07-13</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>Inventering utförd av länsstyrelsen i Kalmar län.</t>
@@ -2425,7 +2258,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Grov, bränd, död björk</t>
+          <t>Bränd, död ek</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr"/>
@@ -2448,37 +2281,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>108690982</v>
+        <v>108690563</v>
       </c>
       <c r="B15" t="n">
-        <v>12405</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>7199</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101141</v>
+        <v>102236</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Glänsande blombagge</t>
+          <t>Grenplattnos</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ischnomera caerulea</t>
+          <t>Pseudeuparius sepicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1792)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2507,10 +2335,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575461.6290098059</v>
+        <v>575452</v>
       </c>
       <c r="R15" t="n">
-        <v>6336284.051757373</v>
+        <v>6336295</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2537,22 +2365,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-05-18</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2571,7 +2389,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Grov, bränd, död björk</t>
+          <t>Bränd, död ek</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr"/>
@@ -2594,42 +2412,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>108691035</v>
+        <v>108690280</v>
       </c>
       <c r="B16" t="n">
-        <v>8395</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9414</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101988</v>
+        <v>105076</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattad lövvedborre</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Xyleborus monographus</t>
+          <t>Sinodendron cylindricum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2653,10 +2466,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575452.1753613513</v>
+        <v>575461</v>
       </c>
       <c r="R16" t="n">
-        <v>6336295.810780574</v>
+        <v>6336284</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2686,19 +2499,9 @@
           <t>2022-05-18</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2717,7 +2520,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bränd, död ek</t>
+          <t>Grov, bränd, död björk</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr"/>
@@ -2740,67 +2543,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>108691047</v>
+        <v>104688033</v>
       </c>
       <c r="B17" t="n">
-        <v>6699</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>12465</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101413</v>
+        <v>105884</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Notolaemus unifasciatus</t>
+          <t>Mordellistena pygmaeola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Latreille, 1804)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
+          <t>Ermisch, 1956</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Finsjöbrännan, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575452.1753613513</v>
+        <v>575416</v>
       </c>
       <c r="R17" t="n">
-        <v>6336295.810780574</v>
+        <v>6336378</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2824,27 +2608,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-05-18</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Inventering utförd av länsstyrelsen i Kalmar län.</t>
+          <t>Insamlade under NCG-träff</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2853,15 +2627,10 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bränd, död ek</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr"/>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
@@ -2873,23 +2642,14 @@
           <t>Olof Persson</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
-        </is>
-      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>108690563</v>
+        <v>104165887</v>
       </c>
       <c r="B18" t="n">
-        <v>7111</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>7673</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2897,56 +2657,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102236</v>
+        <v>106431</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grenplattnos</t>
+          <t>Furuvedvivel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudeuparius sepicola</t>
+          <t>Rhyncolus elongatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
+          <t>(Gyllenhal, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Finsjöbrännan, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575452.1753613513</v>
+        <v>575416</v>
       </c>
       <c r="R18" t="n">
-        <v>6336295.810780574</v>
+        <v>6336378</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2970,27 +2716,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Inventering utförd av länsstyrelsen i Kalmar län.</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2999,15 +2730,10 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Bränd, död ek</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr"/>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
@@ -3019,23 +2745,14 @@
           <t>Olof Persson</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
-        </is>
-      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>108690565</v>
+        <v>106296597</v>
       </c>
       <c r="B19" t="n">
-        <v>5210</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>19997</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3043,21 +2760,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100975</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Ekgrenbock</t>
-        </is>
+        <v>241068</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Exocentrus adspersus</t>
+          <t>Homalocephala bimaculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Mulsant, 1846</t>
+          <t>(Wahlberg, 1838)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3065,19 +2777,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>fönsterfälla</t>
+          <t>malaisefälla</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3086,10 +2793,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575452.1753613513</v>
+        <v>575486</v>
       </c>
       <c r="R19" t="n">
-        <v>6336295.810780574</v>
+        <v>6336324</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3116,27 +2823,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Inventering utförd av länsstyrelsen i Kalmar län.</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3148,21 +2840,15 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Bränd, död ek</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr"/>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Olof Persson</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Olof Persson</t>
+          <t>Via Michael Tholin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -3170,980 +2856,6 @@
           <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>108690253</v>
-      </c>
-      <c r="B20" t="n">
-        <v>6699</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>101413</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Notolaemus unifasciatus</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Latreille, 1804)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Finsjöbrännan, Sm</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>575461.6290098059</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6336284.051757373</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Fliseryd</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2022-05-18</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Inventering utförd av länsstyrelsen i Kalmar län.</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Grov, bränd, död björk</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr"/>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Olof Persson</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Olof Persson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>108690562</v>
-      </c>
-      <c r="B21" t="n">
-        <v>6229</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>100838</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Enfärgad brandsvampbagge</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Diplocoelus fagi</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Chevrolat, 1837)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Finsjöbrännan, Sm</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>575452.1753613513</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6336295.810780574</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Fliseryd</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2022-08-15</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Inventering utförd av länsstyrelsen i Kalmar län.</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bränd, död ek</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr"/>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Olof Persson</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Olof Persson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>108689834</v>
-      </c>
-      <c r="B22" t="n">
-        <v>8209</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>RE</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>101592</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Ekcylinderbagge</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Platypus cylindrus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Fabricius, 1792)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Finsjöbrännan, Sm</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>575452.1753613513</v>
-      </c>
-      <c r="R22" t="n">
-        <v>6336295.810780574</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Fliseryd</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2022-08-15</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2022-09-15</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Inventering utförd av länsstyrelsen i Kalmar län.</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Död, bränd ek</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr"/>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Olof Persson</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Olof Persson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>108690567</v>
-      </c>
-      <c r="B23" t="n">
-        <v>12721</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>101950</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Större sågsvartbagge</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Uloma culinaris</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Finsjöbrännan, Sm</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>575452.1753613513</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6336295.810780574</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Fliseryd</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2022-08-15</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Inventering utförd av länsstyrelsen i Kalmar län.</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Bränd, död ek</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr"/>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Olof Persson</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Olof Persson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>108690280</v>
-      </c>
-      <c r="B24" t="n">
-        <v>9310</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>105076</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Noshornsoxe</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Sinodendron cylindricum</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Finsjöbrännan, Sm</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>575461.6290098059</v>
-      </c>
-      <c r="R24" t="n">
-        <v>6336284.051757373</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Fliseryd</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2022-05-18</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Inventering utförd av länsstyrelsen i Kalmar län.</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Grov, bränd, död björk</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr"/>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Olof Persson</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Olof Persson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>108690591</v>
-      </c>
-      <c r="B25" t="n">
-        <v>8209</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>RE</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>101592</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Ekcylinderbagge</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Platypus cylindrus</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Fabricius, 1792)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Finsjöbrännan, Sm</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>575461.6290098059</v>
-      </c>
-      <c r="R25" t="n">
-        <v>6336284.051757373</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Fliseryd</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2022-08-15</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Inventering utförd av länsstyrelsen i Kalmar län.</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Grov, bränd, död björk</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr"/>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Olof Persson</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Olof Persson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>126839410</v>
-      </c>
-      <c r="B26" t="n">
-        <v>56600</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>100041</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Hasselsnok</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Coronella austriaca</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Laurenti, 1768</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Skvalbäcken, Sm</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>575468</v>
-      </c>
-      <c r="R26" t="n">
-        <v>6336200</v>
-      </c>
-      <c r="S26" t="n">
-        <v>50</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Fliseryd</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Marcus Arnesson</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Marcus Arnesson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41266-2021 artfynd.xlsx
+++ b/artfynd/A 41266-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -775,6 +780,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126839410</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104688012</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
           <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108690566</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
           <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108690562</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1271,6 +1296,11 @@
           <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108690982</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1397,6 +1427,11 @@
           <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108690319</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1512,6 +1547,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104165850</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1643,6 +1683,11 @@
           <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108690325</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1769,6 +1814,11 @@
           <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108690253</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1895,6 +1945,11 @@
           <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108690301</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2026,6 +2081,11 @@
           <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108690564</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2147,6 +2207,11 @@
           <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106295826</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2278,6 +2343,11 @@
           <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108690330</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2409,6 +2479,11 @@
           <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108690563</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2538,6 +2613,11 @@
       <c r="AY16" t="inlineStr">
         <is>
           <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108690280</t>
         </is>
       </c>
     </row>
@@ -2643,6 +2723,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104688033</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2746,6 +2831,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104165887</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2856,8 +2946,33 @@
           <t>Fönsterfälleinventeringar Länsstyrelsen Kalmar län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106296597</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>